--- a/Status_work.xlsx
+++ b/Status_work.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tm/Documents/09_EcoProject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A92825F-F41A-8E44-848B-42E480BC5A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2782B5AE-9839-D74A-88B9-AD0B7D733AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{3AEDEEF5-046A-774E-A62D-875E14033845}"/>
+    <workbookView xWindow="35260" yWindow="620" windowWidth="36400" windowHeight="21680" xr2:uid="{3AEDEEF5-046A-774E-A62D-875E14033845}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>Название задачи</t>
   </si>
@@ -103,6 +103,9 @@
   </si>
   <si>
     <t>to do</t>
+  </si>
+  <si>
+    <t>test for overloading</t>
   </si>
 </sst>
 </file>
@@ -557,15 +560,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66B5E217-3922-5B41-8E04-AF558F0E3049}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58" style="5" customWidth="1"/>
     <col min="2" max="2" width="13.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -576,7 +580,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -587,7 +591,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -595,10 +599,13 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -609,7 +616,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
@@ -620,7 +627,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
@@ -631,7 +638,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -642,7 +649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
@@ -653,7 +660,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>9</v>
       </c>
@@ -664,7 +671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>10</v>
       </c>
@@ -675,7 +682,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
@@ -686,7 +693,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>12</v>
       </c>
@@ -694,10 +701,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>13</v>
       </c>
@@ -708,7 +715,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>14</v>
       </c>
@@ -716,10 +723,10 @@
         <v>4</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>15</v>
       </c>
@@ -727,10 +734,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>16</v>
       </c>
@@ -738,7 +745,7 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="17" x14ac:dyDescent="0.2">
@@ -762,6 +769,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
